--- a/data/trans_dic/Hacinamiento_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/Hacinamiento_R-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación</t>
+          <t>Hogares con dos o más personas por habitación (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,59; 22,73</t>
+          <t>6,67; 21,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,95; 29,71</t>
+          <t>11,82; 29,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,87; 30,27</t>
+          <t>10,86; 30,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,22; 17,56</t>
+          <t>3,44; 16,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,51; 22,11</t>
+          <t>6,47; 22,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,17; 23,17</t>
+          <t>8,42; 22,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,19; 24,46</t>
+          <t>8,1; 25,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,48; 38,36</t>
+          <t>16,59; 37,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,87; 19,64</t>
+          <t>8,39; 19,22</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,49; 22,5</t>
+          <t>11,36; 22,59</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,26; 23,9</t>
+          <t>11,27; 24,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,08; 26,79</t>
+          <t>12,49; 26,53</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,36; 8,86</t>
+          <t>4,13; 8,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,17; 13,01</t>
+          <t>7,06; 13,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,82; 10,59</t>
+          <t>5,88; 10,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,3; 7,97</t>
+          <t>4,27; 8,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,51; 10,13</t>
+          <t>5,46; 9,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,09; 12,69</t>
+          <t>7,35; 12,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,97; 9,38</t>
+          <t>4,98; 9,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,62; 10,27</t>
+          <t>5,89; 10,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,36; 8,42</t>
+          <t>5,45; 8,67</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,03; 11,92</t>
+          <t>8,07; 11,83</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,85; 8,96</t>
+          <t>5,96; 9,12</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,55; 8,49</t>
+          <t>5,52; 8,58</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,35; 8,31</t>
+          <t>2,11; 8,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 11,93</t>
+          <t>3,72; 12,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,07; 11,99</t>
+          <t>4,0; 11,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 9,29</t>
+          <t>2,62; 8,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,29; 12,12</t>
+          <t>4,35; 11,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 9,16</t>
+          <t>2,58; 9,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,94</t>
+          <t>0,96; 5,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 6,05</t>
+          <t>1,29; 6,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,61; 8,29</t>
+          <t>3,81; 8,65</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,78; 9,08</t>
+          <t>3,61; 9,14</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,92; 7,38</t>
+          <t>2,99; 7,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 6,17</t>
+          <t>2,24; 6,07</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,96; 8,53</t>
+          <t>5,06; 8,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,93; 12,53</t>
+          <t>8,05; 12,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,55; 10,48</t>
+          <t>6,66; 10,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,58; 7,73</t>
+          <t>4,5; 7,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,3; 9,94</t>
+          <t>6,36; 10,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,17; 11,56</t>
+          <t>7,33; 11,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,07; 8,45</t>
+          <t>5,07; 8,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,36; 10,31</t>
+          <t>6,52; 10,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,97; 8,62</t>
+          <t>6,0; 8,64</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,28; 11,27</t>
+          <t>8,21; 11,23</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,37; 8,9</t>
+          <t>6,39; 9,04</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,05; 8,67</t>
+          <t>6,01; 8,44</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con dos o más personas por habitación (tasa de respuesta: 99,79%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>7658</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10616</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7637</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4442</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>6553</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8810</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>7935</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>16642</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>14211</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>19425</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>15572</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>21084</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>3735; 12269</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6558; 16335</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4414; 12566</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1853; 9122</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3326; 11345</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5225; 13959</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>4151; 13008</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>10286; 23148</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>9014; 20639</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>13352; 26557</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>10359; 22358</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>14475; 30738</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>19027</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>29605</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>27436</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>27736</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>26655</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>33440</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>26155</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>39948</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>45682</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>63044</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>53590</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>67684</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>12790; 26642</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>21507; 39769</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>20466; 36622</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>19545; 37876</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>19311; 35071</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>24977; 43629</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>18900; 36384</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>30424; 53879</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>36137; 57531</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>51980; 76260</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>43399; 66387</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>53731; 83605</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>6276</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8269</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9651</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7259</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>8943</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7137</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3655</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>5496</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>15220</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>15406</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>13306</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>12756</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2877; 11732</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4349; 14160</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5439; 15477</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3857; 13213</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5373; 14784</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3529; 13605</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1341; 7788</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2337; 10958</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>9902; 22501</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>9152; 23183</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>8233; 19926</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>7385; 19968</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>32961</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>48489</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>44723</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>42151</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>49386</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>37745</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>62086</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>75112</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>97876</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>82468</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>101524</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>25409; 43683</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>38389; 61454</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>34963; 56558</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>29665; 50417</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>33619; 53681</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>39493; 62706</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>28904; 49272</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>49592; 77792</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>61797; 89101</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>83350; 114106</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>70008; 99045</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>85282; 119816</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/Hacinamiento_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/Hacinamiento_R-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,67; 21,91</t>
+          <t>6,89; 22,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,82; 29,44</t>
+          <t>11,43; 28,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,86; 30,92</t>
+          <t>10,55; 29,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,44; 16,93</t>
+          <t>3,2; 17,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,47; 22,09</t>
+          <t>6,43; 20,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,42; 22,48</t>
+          <t>7,98; 22,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,1; 25,39</t>
+          <t>8,54; 26,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,59; 37,33</t>
+          <t>17,13; 37,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,39; 19,22</t>
+          <t>8,64; 19,48</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,36; 22,59</t>
+          <t>11,72; 22,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,27; 24,33</t>
+          <t>11,0; 23,67</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,49; 26,53</t>
+          <t>12,07; 25,35</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,13; 8,6</t>
+          <t>4,25; 8,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,06; 13,05</t>
+          <t>7,17; 12,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,88; 10,52</t>
+          <t>5,91; 10,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 8,28</t>
+          <t>4,27; 8,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,46; 9,92</t>
+          <t>5,44; 9,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,35; 12,84</t>
+          <t>7,21; 13,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,98; 9,58</t>
+          <t>4,83; 9,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,89; 10,43</t>
+          <t>5,55; 10,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,45; 8,67</t>
+          <t>5,38; 8,56</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,07; 11,83</t>
+          <t>8,08; 11,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,96; 9,12</t>
+          <t>5,97; 9,09</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,52; 8,58</t>
+          <t>5,46; 8,55</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 8,59</t>
+          <t>2,26; 8,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,72; 12,12</t>
+          <t>3,5; 11,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,0; 11,38</t>
+          <t>3,92; 11,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,62; 8,96</t>
+          <t>2,49; 9,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,35; 11,97</t>
+          <t>4,16; 11,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,58; 9,94</t>
+          <t>2,47; 9,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,59</t>
+          <t>0,93; 5,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 6,03</t>
+          <t>1,33; 6,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,81; 8,65</t>
+          <t>3,78; 8,84</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,61; 9,14</t>
+          <t>3,67; 9,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,99; 7,24</t>
+          <t>2,93; 7,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 6,07</t>
+          <t>2,22; 6,03</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,06; 8,7</t>
+          <t>4,96; 8,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,05; 12,88</t>
+          <t>8,18; 12,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,66; 10,78</t>
+          <t>6,62; 10,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,5; 7,65</t>
+          <t>4,47; 7,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,36; 10,16</t>
+          <t>6,19; 10,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,33; 11,64</t>
+          <t>7,1; 11,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,07; 8,64</t>
+          <t>5,02; 8,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,52; 10,23</t>
+          <t>6,46; 10,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,0; 8,64</t>
+          <t>5,97; 8,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,21; 11,23</t>
+          <t>8,18; 11,2</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,39; 9,04</t>
+          <t>6,2; 8,78</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,01; 8,44</t>
+          <t>5,95; 8,53</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3735; 12269</t>
+          <t>3861; 12473</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6558; 16335</t>
+          <t>6340; 15859</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4414; 12566</t>
+          <t>4288; 12092</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1853; 9122</t>
+          <t>1726; 9227</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3326; 11345</t>
+          <t>3306; 10623</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5225; 13959</t>
+          <t>4952; 13793</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4151; 13008</t>
+          <t>4376; 13502</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10286; 23148</t>
+          <t>10621; 23521</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9014; 20639</t>
+          <t>9272; 20918</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13352; 26557</t>
+          <t>13777; 26650</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10359; 22358</t>
+          <t>10106; 21751</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14475; 30738</t>
+          <t>13989; 29379</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12790; 26642</t>
+          <t>13165; 26941</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21507; 39769</t>
+          <t>21830; 38086</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20466; 36622</t>
+          <t>20562; 36777</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19545; 37876</t>
+          <t>19521; 37602</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19311; 35071</t>
+          <t>19236; 34629</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24977; 43629</t>
+          <t>24511; 44898</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18900; 36384</t>
+          <t>18360; 35058</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30424; 53879</t>
+          <t>28694; 52562</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36137; 57531</t>
+          <t>35709; 56787</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>51980; 76260</t>
+          <t>52047; 76114</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43399; 66387</t>
+          <t>43422; 66136</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>53731; 83605</t>
+          <t>53189; 83262</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2877; 11732</t>
+          <t>3081; 11237</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4349; 14160</t>
+          <t>4085; 13519</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5439; 15477</t>
+          <t>5334; 15793</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3857; 13213</t>
+          <t>3677; 13446</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5373; 14784</t>
+          <t>5138; 14272</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3529; 13605</t>
+          <t>3387; 13342</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1341; 7788</t>
+          <t>1297; 8241</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2337; 10958</t>
+          <t>2417; 11496</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9902; 22501</t>
+          <t>9834; 22993</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9152; 23183</t>
+          <t>9306; 23412</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8233; 19926</t>
+          <t>8065; 19564</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7385; 19968</t>
+          <t>7320; 19859</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25409; 43683</t>
+          <t>24919; 42812</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>38389; 61454</t>
+          <t>39011; 60340</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34963; 56558</t>
+          <t>34721; 55716</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29665; 50417</t>
+          <t>29421; 50595</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33619; 53681</t>
+          <t>32699; 53374</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>39493; 62706</t>
+          <t>38238; 61357</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28904; 49272</t>
+          <t>28628; 48785</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>49592; 77792</t>
+          <t>49117; 77960</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>61797; 89101</t>
+          <t>61541; 88920</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>83350; 114106</t>
+          <t>83051; 113810</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>70008; 99045</t>
+          <t>67923; 96114</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>85282; 119816</t>
+          <t>84396; 121118</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Hacinamiento_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/Hacinamiento_R-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12,76%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14,19%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>15,49%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>25,69%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>13,67%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>19,13%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>18,79%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8,25%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>12,76%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14,19%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,49%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,89; 22,27</t>
+          <t>6,51; 22,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,43; 28,58</t>
+          <t>8,17; 23,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,55; 29,75</t>
+          <t>8,19; 24,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,2; 17,13</t>
+          <t>16,2; 36,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,43; 20,68</t>
+          <t>7,59; 22,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,98; 22,21</t>
+          <t>11,95; 29,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,54; 26,35</t>
+          <t>9,87; 30,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,13; 37,93</t>
+          <t>5,35; 22,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,64; 19,48</t>
+          <t>8,87; 19,64</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,72; 22,67</t>
+          <t>11,49; 22,5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,0; 23,67</t>
+          <t>11,26; 23,9</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,07; 25,35</t>
+          <t>13,34; 28,09</t>
         </is>
       </c>
     </row>
@@ -789,49 +789,49 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7,54%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9,84%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6,89%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7,57%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>6,14%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>9,72%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>7,88%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,54%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,84%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>6,37%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>6,89%</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>7,73%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>6,89%</t>
-        </is>
-      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
           <t>9,78%</t>
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,25; 8,7</t>
+          <t>5,51; 10,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,17; 12,5</t>
+          <t>7,09; 12,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,91; 10,57</t>
+          <t>4,97; 9,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 8,22</t>
+          <t>5,57; 10,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,44; 9,79</t>
+          <t>4,36; 8,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,21; 13,21</t>
+          <t>7,17; 13,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,83; 9,23</t>
+          <t>5,82; 10,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,55; 10,17</t>
+          <t>4,61; 8,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,38; 8,56</t>
+          <t>5,36; 8,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,08; 11,81</t>
+          <t>8,03; 11,92</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,97; 9,09</t>
+          <t>5,85; 8,96</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,46; 8,55</t>
+          <t>5,59; 8,57</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7,24%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5,21%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>4,6%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>7,08%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>7,09%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,93%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,24%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,21%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,26; 8,23</t>
+          <t>4,29; 12,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,5; 11,57</t>
+          <t>2,48; 9,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 11,61</t>
+          <t>0,94; 5,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 9,12</t>
+          <t>1,14; 5,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,16; 11,55</t>
+          <t>2,35; 8,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,47; 9,75</t>
+          <t>3,79; 11,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,92</t>
+          <t>4,07; 11,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 6,33</t>
+          <t>2,56; 9,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,78; 8,84</t>
+          <t>3,61; 8,29</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,67; 9,23</t>
+          <t>3,78; 9,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,93; 7,11</t>
+          <t>2,92; 7,38</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 6,03</t>
+          <t>2,27; 5,54</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7,97%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,62%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7,85%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>6,56%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>10,17%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>8,52%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,99%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,97%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,17%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,62%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,96; 8,52</t>
+          <t>6,3; 9,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,18; 12,65</t>
+          <t>7,17; 11,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,62; 10,62</t>
+          <t>5,07; 8,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,47; 7,68</t>
+          <t>6,14; 9,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,19; 10,1</t>
+          <t>4,96; 8,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,1; 11,39</t>
+          <t>7,93; 12,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,02; 8,55</t>
+          <t>6,55; 10,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,46; 10,25</t>
+          <t>4,97; 8,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,97; 8,63</t>
+          <t>5,97; 8,62</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,18; 11,2</t>
+          <t>8,28; 11,27</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,2; 8,78</t>
+          <t>6,37; 8,9</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,95; 8,53</t>
+          <t>6,02; 8,56</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>6553</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8810</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7935</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14572</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>7658</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>10616</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>7637</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4442</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>6553</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8810</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7935</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16642</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21084</t>
+          <t>19888</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3861; 12473</t>
+          <t>3345; 11360</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6340; 15859</t>
+          <t>5074; 14388</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4288; 12092</t>
+          <t>4195; 12531</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1726; 9227</t>
+          <t>9188; 20959</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3306; 10623</t>
+          <t>4251; 12729</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4952; 13793</t>
+          <t>6631; 16482</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4376; 13502</t>
+          <t>4013; 12302</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10621; 23521</t>
+          <t>2452; 10190</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9272; 20918</t>
+          <t>9529; 21091</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13777; 26650</t>
+          <t>13511; 26460</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10106; 21751</t>
+          <t>10341; 21956</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13989; 29379</t>
+          <t>13686; 28823</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>26655</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>33440</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>26155</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>36024</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>19027</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>29605</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>27436</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>27736</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>26655</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>33440</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>26155</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>39948</t>
+          <t>27314</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>67684</t>
+          <t>63338</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13165; 26941</t>
+          <t>19494; 35829</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21830; 38086</t>
+          <t>24080; 43136</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20562; 36777</t>
+          <t>18864; 35617</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19521; 37602</t>
+          <t>26478; 48047</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19236; 34629</t>
+          <t>13506; 27423</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24511; 44898</t>
+          <t>21844; 39630</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18360; 35058</t>
+          <t>20240; 36862</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28694; 52562</t>
+          <t>19778; 37090</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35709; 56787</t>
+          <t>35546; 55867</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>52047; 76114</t>
+          <t>51779; 76842</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43422; 66136</t>
+          <t>42613; 65191</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>53189; 83262</t>
+          <t>50538; 77495</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>8943</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7137</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3655</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4318</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>6276</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>8269</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>9651</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7259</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>8943</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>7137</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3655</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5496</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12756</t>
+          <t>11324</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3081; 11237</t>
+          <t>5304; 14971</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4085; 13519</t>
+          <t>3402; 12545</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5334; 15793</t>
+          <t>1314; 8269</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3677; 13446</t>
+          <t>1906; 8654</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5138; 14272</t>
+          <t>3204; 11346</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3387; 13342</t>
+          <t>4426; 13935</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1297; 8241</t>
+          <t>5536; 16307</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2417; 11496</t>
+          <t>3777; 13325</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9834; 22993</t>
+          <t>9385; 21566</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9306; 23412</t>
+          <t>9593; 23028</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8065; 19564</t>
+          <t>8033; 20324</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7320; 19859</t>
+          <t>7149; 17413</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>62</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>42151</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>49386</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>37745</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>54913</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>32961</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>48489</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>44723</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>42151</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>49386</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>37745</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>62086</t>
+          <t>39637</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>101524</t>
+          <t>94550</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24919; 42812</t>
+          <t>33274; 52542</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>39011; 60340</t>
+          <t>38616; 62296</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34721; 55716</t>
+          <t>28893; 48170</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29421; 50595</t>
+          <t>42903; 69325</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32699; 53374</t>
+          <t>24916; 42840</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38238; 61357</t>
+          <t>37802; 59783</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28628; 48785</t>
+          <t>34354; 55005</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>49117; 77960</t>
+          <t>30947; 50229</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>61541; 88920</t>
+          <t>61548; 88815</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>83051; 113810</t>
+          <t>84091; 114490</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>67923; 96114</t>
+          <t>69808; 97438</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>84396; 121118</t>
+          <t>79613; 113201</t>
         </is>
       </c>
     </row>
